--- a/.github/workflows/data/reporte_ssb_cr_bq_interno.xlsx
+++ b/.github/workflows/data/reporte_ssb_cr_bq_interno.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Husband\github\iniciativas\.github\workflows\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017944E4-6A56-4310-9B42-DED0095D1B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4BA64C-1BEA-48E3-A4AE-9D0C4B9DE8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>cr/bqs</t>
   </si>
@@ -40,6 +40,15 @@
   </si>
   <si>
     <t>Saving Account</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>Customer Credit Rating</t>
+  </si>
+  <si>
+    <t>Internal Reporting</t>
   </si>
 </sst>
 </file>
@@ -369,8 +378,8 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.88671875" customWidth="1"/>
-    <col min="3" max="3" width="15.77734375" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -396,7 +405,15 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C3" s="1"/>
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/.github/workflows/data/reporte_ssb_cr_bq_interno.xlsx
+++ b/.github/workflows/data/reporte_ssb_cr_bq_interno.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Husband\github\iniciativas\.github\workflows\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4BA64C-1BEA-48E3-A4AE-9D0C4B9DE8E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9132B736-F921-4845-A08B-02ECE67DA2BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>cr/bqs</t>
   </si>
@@ -42,29 +42,57 @@
     <t>Saving Account</t>
   </si>
   <si>
-    <t>FN</t>
-  </si>
-  <si>
-    <t>Customer Credit Rating</t>
-  </si>
-  <si>
-    <t>Internal Reporting</t>
+    <t>Metodo</t>
+  </si>
+  <si>
+    <t>endpoint</t>
+  </si>
+  <si>
+    <t>Api</t>
+  </si>
+  <si>
+    <t>POST</t>
+  </si>
+  <si>
+    <t>/customer-credit-rating/initiate</t>
+  </si>
+  <si>
+    <t>PUT</t>
+  </si>
+  <si>
+    <t>BQ</t>
+  </si>
+  <si>
+    <t>API BS Customer Credit Rating Paid V1</t>
+  </si>
+  <si>
+    <t>/customer-credit/{id}/internal-reporting</t>
+  </si>
+  <si>
+    <t>Order</t>
+  </si>
+  <si>
+    <t>/customer-credit/{id}/order/initiate</t>
+  </si>
+  <si>
+    <t>BIAN</t>
+  </si>
+  <si>
+    <t>Clasification</t>
+  </si>
+  <si>
+    <t>Credit Card</t>
+  </si>
+  <si>
+    <t>origen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -92,9 +120,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -375,14 +402,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.44140625" customWidth="1"/>
     <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" customWidth="1"/>
+    <col min="6" max="6" width="33.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -392,8 +423,23 @@
       <c r="C1" t="s">
         <v>0</v>
       </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -403,19 +449,76 @@
       <c r="C2" t="s">
         <v>4</v>
       </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/.github/workflows/data/reporte_ssb_cr_bq_interno.xlsx
+++ b/.github/workflows/data/reporte_ssb_cr_bq_interno.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Husband\github\iniciativas\.github\workflows\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9132B736-F921-4845-A08B-02ECE67DA2BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF034D9F-D565-4839-91A8-807F8F4ECB02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,13 +78,13 @@
     <t>BIAN</t>
   </si>
   <si>
-    <t>Clasification</t>
-  </si>
-  <si>
     <t>Credit Card</t>
   </si>
   <si>
     <t>origen</t>
+  </si>
+  <si>
+    <t>dominio</t>
   </si>
 </sst>
 </file>
@@ -433,10 +433,10 @@
         <v>6</v>
       </c>
       <c r="G1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" t="s">
         <v>19</v>
-      </c>
-      <c r="H1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -514,7 +514,7 @@
         <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/.github/workflows/data/reporte_ssb_cr_bq_interno.xlsx
+++ b/.github/workflows/data/reporte_ssb_cr_bq_interno.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Husband\github\iniciativas\.github\workflows\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF034D9F-D565-4839-91A8-807F8F4ECB02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9338907-3A58-487A-817C-143AAF3F1811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>cr/bqs</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>dominio</t>
+  </si>
+  <si>
+    <t>SD 001011 Payment Initiation Credit Card</t>
+  </si>
+  <si>
+    <t>BQ Quote</t>
+  </si>
+  <si>
+    <t>API BS Payment Initiation Credit Card V1</t>
+  </si>
+  <si>
+    <t>/payment-initiations/{id}/quotes/{quoteId}/update</t>
   </si>
 </sst>
 </file>
@@ -402,14 +414,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="34.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.44140625" customWidth="1"/>
     <col min="4" max="4" width="32.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.77734375" customWidth="1"/>
-    <col min="6" max="6" width="33.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="43" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -517,6 +529,32 @@
         <v>17</v>
       </c>
     </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
